--- a/项目库.xlsx
+++ b/项目库.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\zhong\PyCharm\YKABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FAA5D5-1306-4BD3-99BC-95A06FD8FE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66CDE99-D4CB-47C5-B340-692594DF4060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B4AD8DE-DEA2-44E1-BABE-E39F8463801E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7195" uniqueCount="2959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7258" uniqueCount="2987">
   <si>
     <t>证券编号</t>
   </si>
@@ -8916,6 +8916,90 @@
   </si>
   <si>
     <t>082581153.IB</t>
+  </si>
+  <si>
+    <t>鸿富2026-1</t>
+  </si>
+  <si>
+    <t>26鸿富1C</t>
+  </si>
+  <si>
+    <t>2689082.IB</t>
+  </si>
+  <si>
+    <t>鸿富2026-2</t>
+  </si>
+  <si>
+    <t>26鸿富2C</t>
+  </si>
+  <si>
+    <t>2689084.IB</t>
+  </si>
+  <si>
+    <t>国健租赁第11期</t>
+  </si>
+  <si>
+    <t>国健11B</t>
+  </si>
+  <si>
+    <t>268605.SH</t>
+  </si>
+  <si>
+    <t>国健租赁</t>
+  </si>
+  <si>
+    <t>建欣2026-2</t>
+  </si>
+  <si>
+    <t>26建欣2C</t>
+  </si>
+  <si>
+    <t>2689096.IB</t>
+  </si>
+  <si>
+    <t>中誉至诚2026-3</t>
+  </si>
+  <si>
+    <t>26中誉至诚3C</t>
+  </si>
+  <si>
+    <t>2689092.IB</t>
+  </si>
+  <si>
+    <t>尚赢2号6期</t>
+  </si>
+  <si>
+    <t>尚赢贰6C</t>
+  </si>
+  <si>
+    <t>268682.SH</t>
+  </si>
+  <si>
+    <t>建欣2026-3</t>
+  </si>
+  <si>
+    <t>26建欣3C</t>
+  </si>
+  <si>
+    <t>2689098.IB</t>
+  </si>
+  <si>
+    <t>美满生意2025年1期1号-招证</t>
+  </si>
+  <si>
+    <t>7美意1次</t>
+  </si>
+  <si>
+    <t>268634.SH</t>
+  </si>
+  <si>
+    <t>中誉至诚2026-4</t>
+  </si>
+  <si>
+    <t>26中誉至诚4C</t>
+  </si>
+  <si>
+    <t>2689094.SH</t>
   </si>
 </sst>
 </file>
@@ -9314,7 +9398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C76155E-453F-4668-B0ED-1B0E36401906}">
-  <dimension ref="A1:N959"/>
+  <dimension ref="A1:N968"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="5" max="5" width="11.5625" bestFit="1" customWidth="1"/>
@@ -48404,6 +48488,357 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
+    <row r="960" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A960">
+        <v>959</v>
+      </c>
+      <c r="B960" t="s">
+        <v>2959</v>
+      </c>
+      <c r="C960" t="s">
+        <v>2960</v>
+      </c>
+      <c r="D960" t="s">
+        <v>2961</v>
+      </c>
+      <c r="E960">
+        <v>121000000</v>
+      </c>
+      <c r="F960" t="s">
+        <v>56</v>
+      </c>
+      <c r="G960" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H960" t="s">
+        <v>29</v>
+      </c>
+      <c r="I960" t="s">
+        <v>35</v>
+      </c>
+      <c r="J960" s="1">
+        <v>47871</v>
+      </c>
+      <c r="L960">
+        <v>103</v>
+      </c>
+      <c r="M960">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="961" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A961">
+        <v>960</v>
+      </c>
+      <c r="B961" t="s">
+        <v>2962</v>
+      </c>
+      <c r="C961" t="s">
+        <v>2963</v>
+      </c>
+      <c r="D961" t="s">
+        <v>2964</v>
+      </c>
+      <c r="E961">
+        <v>42000000</v>
+      </c>
+      <c r="F961" t="s">
+        <v>42</v>
+      </c>
+      <c r="G961" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H961" t="s">
+        <v>29</v>
+      </c>
+      <c r="I961" t="s">
+        <v>35</v>
+      </c>
+      <c r="J961" s="1">
+        <v>47871</v>
+      </c>
+      <c r="L961">
+        <v>102</v>
+      </c>
+      <c r="M961">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="962" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A962">
+        <v>961</v>
+      </c>
+      <c r="B962" t="s">
+        <v>2965</v>
+      </c>
+      <c r="C962" t="s">
+        <v>2966</v>
+      </c>
+      <c r="D962" t="s">
+        <v>2967</v>
+      </c>
+      <c r="E962">
+        <v>55000000</v>
+      </c>
+      <c r="F962" t="s">
+        <v>623</v>
+      </c>
+      <c r="G962" t="s">
+        <v>2968</v>
+      </c>
+      <c r="H962" t="s">
+        <v>19</v>
+      </c>
+      <c r="I962" t="s">
+        <v>35</v>
+      </c>
+      <c r="J962" s="1">
+        <v>47056</v>
+      </c>
+      <c r="L962">
+        <v>100</v>
+      </c>
+      <c r="M962">
+        <v>100</v>
+      </c>
+      <c r="N962" s="2">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="963" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A963">
+        <v>962</v>
+      </c>
+      <c r="B963" t="s">
+        <v>2969</v>
+      </c>
+      <c r="C963" t="s">
+        <v>2970</v>
+      </c>
+      <c r="D963" t="s">
+        <v>2971</v>
+      </c>
+      <c r="E963">
+        <v>24000000</v>
+      </c>
+      <c r="F963" t="s">
+        <v>87</v>
+      </c>
+      <c r="G963" t="s">
+        <v>43</v>
+      </c>
+      <c r="H963" t="s">
+        <v>29</v>
+      </c>
+      <c r="I963" t="s">
+        <v>35</v>
+      </c>
+      <c r="J963" s="1">
+        <v>47144</v>
+      </c>
+      <c r="L963">
+        <v>100</v>
+      </c>
+      <c r="M963">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="964" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A964">
+        <v>963</v>
+      </c>
+      <c r="B964" t="s">
+        <v>2972</v>
+      </c>
+      <c r="C964" t="s">
+        <v>2973</v>
+      </c>
+      <c r="D964" t="s">
+        <v>2974</v>
+      </c>
+      <c r="E964">
+        <v>148000000</v>
+      </c>
+      <c r="F964" t="s">
+        <v>27</v>
+      </c>
+      <c r="G964" t="s">
+        <v>67</v>
+      </c>
+      <c r="H964" t="s">
+        <v>29</v>
+      </c>
+      <c r="I964" t="s">
+        <v>35</v>
+      </c>
+      <c r="J964" s="1">
+        <v>47203</v>
+      </c>
+      <c r="L964">
+        <v>108</v>
+      </c>
+      <c r="M964">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="965" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A965">
+        <v>964</v>
+      </c>
+      <c r="B965" t="s">
+        <v>2975</v>
+      </c>
+      <c r="C965" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D965" t="s">
+        <v>2977</v>
+      </c>
+      <c r="E965">
+        <v>70000000</v>
+      </c>
+      <c r="F965" t="s">
+        <v>117</v>
+      </c>
+      <c r="G965" t="s">
+        <v>289</v>
+      </c>
+      <c r="H965" t="s">
+        <v>19</v>
+      </c>
+      <c r="I965" t="s">
+        <v>35</v>
+      </c>
+      <c r="J965" s="1">
+        <v>46804</v>
+      </c>
+      <c r="L965">
+        <v>100</v>
+      </c>
+      <c r="M965">
+        <v>100</v>
+      </c>
+      <c r="N965" s="2">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="966" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A966">
+        <v>965</v>
+      </c>
+      <c r="B966" t="s">
+        <v>2978</v>
+      </c>
+      <c r="C966" t="s">
+        <v>2979</v>
+      </c>
+      <c r="D966" t="s">
+        <v>2980</v>
+      </c>
+      <c r="E966">
+        <v>260000000</v>
+      </c>
+      <c r="F966" t="s">
+        <v>42</v>
+      </c>
+      <c r="G966" t="s">
+        <v>43</v>
+      </c>
+      <c r="H966" t="s">
+        <v>29</v>
+      </c>
+      <c r="I966" t="s">
+        <v>35</v>
+      </c>
+      <c r="J966" s="1">
+        <v>48786</v>
+      </c>
+      <c r="L966">
+        <v>100</v>
+      </c>
+      <c r="M966">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="967" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A967">
+        <v>966</v>
+      </c>
+      <c r="B967" t="s">
+        <v>2981</v>
+      </c>
+      <c r="C967" t="s">
+        <v>2982</v>
+      </c>
+      <c r="D967" t="s">
+        <v>2983</v>
+      </c>
+      <c r="E967">
+        <v>193500000</v>
+      </c>
+      <c r="F967" t="s">
+        <v>117</v>
+      </c>
+      <c r="G967" t="s">
+        <v>186</v>
+      </c>
+      <c r="H967" t="s">
+        <v>19</v>
+      </c>
+      <c r="I967" t="s">
+        <v>35</v>
+      </c>
+      <c r="J967" s="1">
+        <v>47266</v>
+      </c>
+      <c r="L967">
+        <v>100</v>
+      </c>
+      <c r="M967">
+        <v>100</v>
+      </c>
+      <c r="N967" s="2">
+        <v>4.7E-2</v>
+      </c>
+    </row>
+    <row r="968" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A968">
+        <v>967</v>
+      </c>
+      <c r="B968" t="s">
+        <v>2984</v>
+      </c>
+      <c r="C968" t="s">
+        <v>2985</v>
+      </c>
+      <c r="D968" t="s">
+        <v>2986</v>
+      </c>
+      <c r="E968">
+        <v>270000000</v>
+      </c>
+      <c r="F968" t="s">
+        <v>33</v>
+      </c>
+      <c r="G968" t="s">
+        <v>67</v>
+      </c>
+      <c r="H968" t="s">
+        <v>29</v>
+      </c>
+      <c r="I968" t="s">
+        <v>35</v>
+      </c>
+      <c r="J968" s="1">
+        <v>49001</v>
+      </c>
+      <c r="L968">
+        <v>100</v>
+      </c>
+      <c r="M968">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/项目库.xlsx
+++ b/项目库.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\zhong\PyCharm\YKABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66CDE99-D4CB-47C5-B340-692594DF4060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D51A8A1-FF27-46BA-AF92-F0278EB33D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B4AD8DE-DEA2-44E1-BABE-E39F8463801E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7258" uniqueCount="2987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7265" uniqueCount="2990">
   <si>
     <t>证券编号</t>
   </si>
@@ -8462,9 +8462,6 @@
     <t>082680178.IB</t>
   </si>
   <si>
-    <t>26蔚能电池ABN001BC优先A1</t>
-  </si>
-  <si>
     <t>082680176.IB</t>
   </si>
   <si>
@@ -9000,6 +8997,18 @@
   </si>
   <si>
     <t>2689094.SH</t>
+  </si>
+  <si>
+    <t>26蔚能电池ABN001BC优先A1(绿色)</t>
+  </si>
+  <si>
+    <t>金采8号1期</t>
+  </si>
+  <si>
+    <t>金采801B</t>
+  </si>
+  <si>
+    <t>268348.SH</t>
   </si>
 </sst>
 </file>
@@ -9398,7 +9407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C76155E-453F-4668-B0ED-1B0E36401906}">
-  <dimension ref="A1:N968"/>
+  <dimension ref="A1:N969"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="5" max="5" width="11.5625" bestFit="1" customWidth="1"/>
@@ -46397,10 +46406,10 @@
         <v>2804</v>
       </c>
       <c r="C908" t="s">
+        <v>2986</v>
+      </c>
+      <c r="D908" t="s">
         <v>2807</v>
-      </c>
-      <c r="D908" t="s">
-        <v>2808</v>
       </c>
       <c r="E908">
         <v>490000000</v>
@@ -46432,13 +46441,13 @@
         <v>908</v>
       </c>
       <c r="B909" t="s">
+        <v>2808</v>
+      </c>
+      <c r="C909" t="s">
         <v>2809</v>
       </c>
-      <c r="C909" t="s">
+      <c r="D909" t="s">
         <v>2810</v>
-      </c>
-      <c r="D909" t="s">
-        <v>2811</v>
       </c>
       <c r="E909">
         <v>40000000</v>
@@ -46470,13 +46479,13 @@
         <v>909</v>
       </c>
       <c r="B910" t="s">
+        <v>2811</v>
+      </c>
+      <c r="C910" t="s">
         <v>2812</v>
       </c>
-      <c r="C910" t="s">
+      <c r="D910" t="s">
         <v>2813</v>
-      </c>
-      <c r="D910" t="s">
-        <v>2814</v>
       </c>
       <c r="E910">
         <v>48000000</v>
@@ -46508,13 +46517,13 @@
         <v>910</v>
       </c>
       <c r="B911" t="s">
+        <v>2814</v>
+      </c>
+      <c r="C911" t="s">
         <v>2815</v>
       </c>
-      <c r="C911" t="s">
+      <c r="D911" t="s">
         <v>2816</v>
-      </c>
-      <c r="D911" t="s">
-        <v>2817</v>
       </c>
       <c r="E911">
         <v>60000000</v>
@@ -46549,13 +46558,13 @@
         <v>911</v>
       </c>
       <c r="B912" t="s">
+        <v>2817</v>
+      </c>
+      <c r="C912" t="s">
         <v>2818</v>
       </c>
-      <c r="C912" t="s">
+      <c r="D912" t="s">
         <v>2819</v>
-      </c>
-      <c r="D912" t="s">
-        <v>2820</v>
       </c>
       <c r="E912">
         <v>100000000</v>
@@ -46590,13 +46599,13 @@
         <v>912</v>
       </c>
       <c r="B913" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C913" t="s">
         <v>2821</v>
       </c>
-      <c r="C913" t="s">
+      <c r="D913" t="s">
         <v>2822</v>
-      </c>
-      <c r="D913" t="s">
-        <v>2823</v>
       </c>
       <c r="E913">
         <v>63000000</v>
@@ -46631,13 +46640,13 @@
         <v>913</v>
       </c>
       <c r="B914" t="s">
+        <v>2823</v>
+      </c>
+      <c r="C914" t="s">
         <v>2824</v>
       </c>
-      <c r="C914" t="s">
+      <c r="D914" t="s">
         <v>2825</v>
-      </c>
-      <c r="D914" t="s">
-        <v>2826</v>
       </c>
       <c r="E914">
         <v>6800000</v>
@@ -46646,7 +46655,7 @@
         <v>27</v>
       </c>
       <c r="G914" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
       <c r="H914" t="s">
         <v>29</v>
@@ -46672,13 +46681,13 @@
         <v>914</v>
       </c>
       <c r="B915" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
       <c r="C915" t="s">
+        <v>2827</v>
+      </c>
+      <c r="D915" t="s">
         <v>2828</v>
-      </c>
-      <c r="D915" t="s">
-        <v>2829</v>
       </c>
       <c r="E915">
         <v>3000000</v>
@@ -46687,7 +46696,7 @@
         <v>27</v>
       </c>
       <c r="G915" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
       <c r="H915" t="s">
         <v>29</v>
@@ -46713,13 +46722,13 @@
         <v>915</v>
       </c>
       <c r="B916" t="s">
+        <v>2829</v>
+      </c>
+      <c r="C916" t="s">
         <v>2830</v>
       </c>
-      <c r="C916" t="s">
+      <c r="D916" t="s">
         <v>2831</v>
-      </c>
-      <c r="D916" t="s">
-        <v>2832</v>
       </c>
       <c r="E916">
         <v>40000000</v>
@@ -46751,13 +46760,13 @@
         <v>916</v>
       </c>
       <c r="B917" t="s">
+        <v>2832</v>
+      </c>
+      <c r="C917" t="s">
         <v>2833</v>
       </c>
-      <c r="C917" t="s">
+      <c r="D917" t="s">
         <v>2834</v>
-      </c>
-      <c r="D917" t="s">
-        <v>2835</v>
       </c>
       <c r="E917">
         <v>161000000</v>
@@ -46789,13 +46798,13 @@
         <v>917</v>
       </c>
       <c r="B918" t="s">
+        <v>2835</v>
+      </c>
+      <c r="C918" t="s">
         <v>2836</v>
       </c>
-      <c r="C918" t="s">
+      <c r="D918" t="s">
         <v>2837</v>
-      </c>
-      <c r="D918" t="s">
-        <v>2838</v>
       </c>
       <c r="E918">
         <v>285000000</v>
@@ -46830,13 +46839,13 @@
         <v>918</v>
       </c>
       <c r="B919" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C919" t="s">
         <v>2839</v>
       </c>
-      <c r="C919" t="s">
+      <c r="D919" t="s">
         <v>2840</v>
-      </c>
-      <c r="D919" t="s">
-        <v>2841</v>
       </c>
       <c r="E919">
         <v>126000000</v>
@@ -46871,13 +46880,13 @@
         <v>919</v>
       </c>
       <c r="B920" t="s">
+        <v>2841</v>
+      </c>
+      <c r="C920" t="s">
         <v>2842</v>
       </c>
-      <c r="C920" t="s">
+      <c r="D920" t="s">
         <v>2843</v>
-      </c>
-      <c r="D920" t="s">
-        <v>2844</v>
       </c>
       <c r="E920">
         <v>390000000</v>
@@ -46912,13 +46921,13 @@
         <v>920</v>
       </c>
       <c r="B921" t="s">
+        <v>2844</v>
+      </c>
+      <c r="C921" t="s">
         <v>2845</v>
       </c>
-      <c r="C921" t="s">
+      <c r="D921" t="s">
         <v>2846</v>
-      </c>
-      <c r="D921" t="s">
-        <v>2847</v>
       </c>
       <c r="E921">
         <v>80000000</v>
@@ -46953,13 +46962,13 @@
         <v>921</v>
       </c>
       <c r="B922" t="s">
+        <v>2847</v>
+      </c>
+      <c r="C922" t="s">
         <v>2848</v>
       </c>
-      <c r="C922" t="s">
+      <c r="D922" t="s">
         <v>2849</v>
-      </c>
-      <c r="D922" t="s">
-        <v>2850</v>
       </c>
       <c r="E922">
         <v>120000000</v>
@@ -46994,13 +47003,13 @@
         <v>922</v>
       </c>
       <c r="B923" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C923" t="s">
         <v>2851</v>
       </c>
-      <c r="C923" t="s">
+      <c r="D923" t="s">
         <v>2852</v>
-      </c>
-      <c r="D923" t="s">
-        <v>2853</v>
       </c>
       <c r="E923">
         <v>227000000</v>
@@ -47035,13 +47044,13 @@
         <v>923</v>
       </c>
       <c r="B924" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C924" t="s">
         <v>2854</v>
       </c>
-      <c r="C924" t="s">
+      <c r="D924" t="s">
         <v>2855</v>
-      </c>
-      <c r="D924" t="s">
-        <v>2856</v>
       </c>
       <c r="E924">
         <v>97000000</v>
@@ -47076,13 +47085,13 @@
         <v>924</v>
       </c>
       <c r="B925" t="s">
+        <v>2856</v>
+      </c>
+      <c r="C925" t="s">
         <v>2857</v>
       </c>
-      <c r="C925" t="s">
+      <c r="D925" t="s">
         <v>2858</v>
-      </c>
-      <c r="D925" t="s">
-        <v>2859</v>
       </c>
       <c r="E925">
         <v>98000000</v>
@@ -47117,13 +47126,13 @@
         <v>925</v>
       </c>
       <c r="B926" t="s">
+        <v>2859</v>
+      </c>
+      <c r="C926" t="s">
         <v>2860</v>
       </c>
-      <c r="C926" t="s">
+      <c r="D926" t="s">
         <v>2861</v>
-      </c>
-      <c r="D926" t="s">
-        <v>2862</v>
       </c>
       <c r="E926">
         <v>250000000</v>
@@ -47158,13 +47167,13 @@
         <v>926</v>
       </c>
       <c r="B927" t="s">
+        <v>2862</v>
+      </c>
+      <c r="C927" t="s">
         <v>2863</v>
       </c>
-      <c r="C927" t="s">
+      <c r="D927" t="s">
         <v>2864</v>
-      </c>
-      <c r="D927" t="s">
-        <v>2865</v>
       </c>
       <c r="E927">
         <v>96000000</v>
@@ -47199,13 +47208,13 @@
         <v>927</v>
       </c>
       <c r="B928" t="s">
+        <v>2865</v>
+      </c>
+      <c r="C928" t="s">
         <v>2866</v>
       </c>
-      <c r="C928" t="s">
+      <c r="D928" t="s">
         <v>2867</v>
-      </c>
-      <c r="D928" t="s">
-        <v>2868</v>
       </c>
       <c r="E928">
         <v>202000000</v>
@@ -47240,13 +47249,13 @@
         <v>928</v>
       </c>
       <c r="B929" t="s">
+        <v>2868</v>
+      </c>
+      <c r="C929" t="s">
         <v>2869</v>
       </c>
-      <c r="C929" t="s">
+      <c r="D929" t="s">
         <v>2870</v>
-      </c>
-      <c r="D929" t="s">
-        <v>2871</v>
       </c>
       <c r="E929">
         <v>63000000</v>
@@ -47281,13 +47290,13 @@
         <v>929</v>
       </c>
       <c r="B930" t="s">
+        <v>2871</v>
+      </c>
+      <c r="C930" t="s">
         <v>2872</v>
       </c>
-      <c r="C930" t="s">
+      <c r="D930" t="s">
         <v>2873</v>
-      </c>
-      <c r="D930" t="s">
-        <v>2874</v>
       </c>
       <c r="E930">
         <v>45000000</v>
@@ -47322,13 +47331,13 @@
         <v>930</v>
       </c>
       <c r="B931" t="s">
+        <v>2874</v>
+      </c>
+      <c r="C931" t="s">
         <v>2875</v>
       </c>
-      <c r="C931" t="s">
+      <c r="D931" t="s">
         <v>2876</v>
-      </c>
-      <c r="D931" t="s">
-        <v>2877</v>
       </c>
       <c r="E931">
         <v>114000000</v>
@@ -47337,7 +47346,7 @@
         <v>2614</v>
       </c>
       <c r="G931" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="H931" t="s">
         <v>19</v>
@@ -47360,13 +47369,13 @@
         <v>931</v>
       </c>
       <c r="B932" t="s">
+        <v>2878</v>
+      </c>
+      <c r="C932" t="s">
         <v>2879</v>
       </c>
-      <c r="C932" t="s">
+      <c r="D932" t="s">
         <v>2880</v>
-      </c>
-      <c r="D932" t="s">
-        <v>2881</v>
       </c>
       <c r="E932">
         <v>1000000</v>
@@ -47401,13 +47410,13 @@
         <v>932</v>
       </c>
       <c r="B933" t="s">
+        <v>2881</v>
+      </c>
+      <c r="C933" t="s">
         <v>2882</v>
       </c>
-      <c r="C933" t="s">
+      <c r="D933" t="s">
         <v>2883</v>
-      </c>
-      <c r="D933" t="s">
-        <v>2884</v>
       </c>
       <c r="E933">
         <v>36000000</v>
@@ -47442,19 +47451,19 @@
         <v>933</v>
       </c>
       <c r="B934" t="s">
+        <v>2884</v>
+      </c>
+      <c r="C934" t="s">
         <v>2885</v>
       </c>
-      <c r="C934" t="s">
+      <c r="D934" t="s">
         <v>2886</v>
-      </c>
-      <c r="D934" t="s">
-        <v>2887</v>
       </c>
       <c r="E934">
         <v>30000000</v>
       </c>
       <c r="F934" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="G934" t="s">
         <v>624</v>
@@ -47483,13 +47492,13 @@
         <v>934</v>
       </c>
       <c r="B935" t="s">
+        <v>2888</v>
+      </c>
+      <c r="C935" t="s">
         <v>2889</v>
       </c>
-      <c r="C935" t="s">
+      <c r="D935" t="s">
         <v>2890</v>
-      </c>
-      <c r="D935" t="s">
-        <v>2891</v>
       </c>
       <c r="E935">
         <v>25000000</v>
@@ -47524,13 +47533,13 @@
         <v>935</v>
       </c>
       <c r="B936" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="C936" t="s">
+        <v>2891</v>
+      </c>
+      <c r="D936" t="s">
         <v>2892</v>
-      </c>
-      <c r="D936" t="s">
-        <v>2893</v>
       </c>
       <c r="E936">
         <v>40000000</v>
@@ -47565,13 +47574,13 @@
         <v>936</v>
       </c>
       <c r="B937" t="s">
+        <v>2893</v>
+      </c>
+      <c r="C937" t="s">
         <v>2894</v>
       </c>
-      <c r="C937" t="s">
+      <c r="D937" t="s">
         <v>2895</v>
-      </c>
-      <c r="D937" t="s">
-        <v>2896</v>
       </c>
       <c r="E937">
         <v>30000000</v>
@@ -47606,13 +47615,13 @@
         <v>937</v>
       </c>
       <c r="B938" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="C938" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D938" t="s">
         <v>2897</v>
-      </c>
-      <c r="D938" t="s">
-        <v>2898</v>
       </c>
       <c r="E938">
         <v>18000000</v>
@@ -47647,13 +47656,13 @@
         <v>938</v>
       </c>
       <c r="B939" t="s">
+        <v>2898</v>
+      </c>
+      <c r="C939" t="s">
         <v>2899</v>
       </c>
-      <c r="C939" t="s">
+      <c r="D939" t="s">
         <v>2900</v>
-      </c>
-      <c r="D939" t="s">
-        <v>2901</v>
       </c>
       <c r="E939">
         <v>86500000</v>
@@ -47662,7 +47671,7 @@
         <v>623</v>
       </c>
       <c r="G939" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="H939" t="s">
         <v>19</v>
@@ -47688,13 +47697,13 @@
         <v>939</v>
       </c>
       <c r="B940" t="s">
+        <v>2902</v>
+      </c>
+      <c r="C940" t="s">
         <v>2903</v>
       </c>
-      <c r="C940" t="s">
+      <c r="D940" t="s">
         <v>2904</v>
-      </c>
-      <c r="D940" t="s">
-        <v>2905</v>
       </c>
       <c r="E940">
         <v>144000000</v>
@@ -47703,7 +47712,7 @@
         <v>623</v>
       </c>
       <c r="G940" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="H940" t="s">
         <v>19</v>
@@ -47729,13 +47738,13 @@
         <v>940</v>
       </c>
       <c r="B941" t="s">
+        <v>2905</v>
+      </c>
+      <c r="C941" t="s">
         <v>2906</v>
       </c>
-      <c r="C941" t="s">
+      <c r="D941" t="s">
         <v>2907</v>
-      </c>
-      <c r="D941" t="s">
-        <v>2908</v>
       </c>
       <c r="E941">
         <v>87000000</v>
@@ -47770,13 +47779,13 @@
         <v>941</v>
       </c>
       <c r="B942" t="s">
+        <v>2908</v>
+      </c>
+      <c r="C942" t="s">
         <v>2909</v>
       </c>
-      <c r="C942" t="s">
+      <c r="D942" t="s">
         <v>2910</v>
-      </c>
-      <c r="D942" t="s">
-        <v>2911</v>
       </c>
       <c r="E942">
         <v>167000000</v>
@@ -47811,13 +47820,13 @@
         <v>942</v>
       </c>
       <c r="B943" t="s">
+        <v>2911</v>
+      </c>
+      <c r="C943" t="s">
         <v>2912</v>
       </c>
-      <c r="C943" t="s">
+      <c r="D943" t="s">
         <v>2913</v>
-      </c>
-      <c r="D943" t="s">
-        <v>2914</v>
       </c>
       <c r="E943">
         <v>60000000</v>
@@ -47852,13 +47861,13 @@
         <v>943</v>
       </c>
       <c r="B944" t="s">
+        <v>2914</v>
+      </c>
+      <c r="C944" t="s">
         <v>2915</v>
       </c>
-      <c r="C944" t="s">
+      <c r="D944" t="s">
         <v>2916</v>
-      </c>
-      <c r="D944" t="s">
-        <v>2917</v>
       </c>
       <c r="E944">
         <v>63000000</v>
@@ -47890,13 +47899,13 @@
         <v>944</v>
       </c>
       <c r="B945" t="s">
+        <v>2917</v>
+      </c>
+      <c r="C945" t="s">
         <v>2918</v>
       </c>
-      <c r="C945" t="s">
+      <c r="D945" t="s">
         <v>2919</v>
-      </c>
-      <c r="D945" t="s">
-        <v>2920</v>
       </c>
       <c r="E945">
         <v>508000000</v>
@@ -47928,13 +47937,13 @@
         <v>945</v>
       </c>
       <c r="B946" t="s">
+        <v>2920</v>
+      </c>
+      <c r="C946" t="s">
         <v>2921</v>
       </c>
-      <c r="C946" t="s">
+      <c r="D946" t="s">
         <v>2922</v>
-      </c>
-      <c r="D946" t="s">
-        <v>2923</v>
       </c>
       <c r="E946">
         <v>201000000</v>
@@ -47966,13 +47975,13 @@
         <v>946</v>
       </c>
       <c r="B947" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="C947" t="s">
+        <v>2923</v>
+      </c>
+      <c r="D947" t="s">
         <v>2924</v>
-      </c>
-      <c r="D947" t="s">
-        <v>2925</v>
       </c>
       <c r="E947">
         <v>75000000</v>
@@ -48001,13 +48010,13 @@
         <v>947</v>
       </c>
       <c r="B948" t="s">
+        <v>2925</v>
+      </c>
+      <c r="C948" t="s">
         <v>2926</v>
       </c>
-      <c r="C948" t="s">
+      <c r="D948" t="s">
         <v>2927</v>
-      </c>
-      <c r="D948" t="s">
-        <v>2928</v>
       </c>
       <c r="E948">
         <v>589000000</v>
@@ -48016,7 +48025,7 @@
         <v>103</v>
       </c>
       <c r="G948" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="H948" t="s">
         <v>19</v>
@@ -48042,13 +48051,13 @@
         <v>948</v>
       </c>
       <c r="B949" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="C949" t="s">
+        <v>2929</v>
+      </c>
+      <c r="D949" t="s">
         <v>2930</v>
-      </c>
-      <c r="D949" t="s">
-        <v>2931</v>
       </c>
       <c r="E949">
         <v>30000000</v>
@@ -48057,7 +48066,7 @@
         <v>103</v>
       </c>
       <c r="G949" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="H949" t="s">
         <v>19</v>
@@ -48083,13 +48092,13 @@
         <v>949</v>
       </c>
       <c r="B950" t="s">
+        <v>2931</v>
+      </c>
+      <c r="C950" t="s">
         <v>2932</v>
       </c>
-      <c r="C950" t="s">
+      <c r="D950" t="s">
         <v>2933</v>
-      </c>
-      <c r="D950" t="s">
-        <v>2934</v>
       </c>
       <c r="E950">
         <v>20000000</v>
@@ -48124,13 +48133,13 @@
         <v>950</v>
       </c>
       <c r="B951" t="s">
+        <v>2934</v>
+      </c>
+      <c r="C951" t="s">
         <v>2935</v>
       </c>
-      <c r="C951" t="s">
+      <c r="D951" t="s">
         <v>2936</v>
-      </c>
-      <c r="D951" t="s">
-        <v>2937</v>
       </c>
       <c r="E951">
         <v>20000000</v>
@@ -48165,13 +48174,13 @@
         <v>951</v>
       </c>
       <c r="B952" t="s">
+        <v>2937</v>
+      </c>
+      <c r="C952" t="s">
         <v>2938</v>
       </c>
-      <c r="C952" t="s">
+      <c r="D952" t="s">
         <v>2939</v>
-      </c>
-      <c r="D952" t="s">
-        <v>2940</v>
       </c>
       <c r="E952">
         <v>30000000</v>
@@ -48206,13 +48215,13 @@
         <v>952</v>
       </c>
       <c r="B953" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="C953" t="s">
+        <v>2940</v>
+      </c>
+      <c r="D953" t="s">
         <v>2941</v>
-      </c>
-      <c r="D953" t="s">
-        <v>2942</v>
       </c>
       <c r="E953">
         <v>18000000</v>
@@ -48247,13 +48256,13 @@
         <v>953</v>
       </c>
       <c r="B954" t="s">
+        <v>2942</v>
+      </c>
+      <c r="C954" t="s">
         <v>2943</v>
       </c>
-      <c r="C954" t="s">
+      <c r="D954" t="s">
         <v>2944</v>
-      </c>
-      <c r="D954" t="s">
-        <v>2945</v>
       </c>
       <c r="E954">
         <v>250000000</v>
@@ -48288,13 +48297,13 @@
         <v>954</v>
       </c>
       <c r="B955" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="C955" t="s">
+        <v>2945</v>
+      </c>
+      <c r="D955" t="s">
         <v>2946</v>
-      </c>
-      <c r="D955" t="s">
-        <v>2947</v>
       </c>
       <c r="E955">
         <v>180000000</v>
@@ -48329,13 +48338,13 @@
         <v>955</v>
       </c>
       <c r="B956" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="C956" t="s">
+        <v>2947</v>
+      </c>
+      <c r="D956" t="s">
         <v>2948</v>
-      </c>
-      <c r="D956" t="s">
-        <v>2949</v>
       </c>
       <c r="E956">
         <v>60000000</v>
@@ -48370,13 +48379,13 @@
         <v>956</v>
       </c>
       <c r="B957" t="s">
+        <v>2949</v>
+      </c>
+      <c r="C957" t="s">
         <v>2950</v>
       </c>
-      <c r="C957" t="s">
+      <c r="D957" t="s">
         <v>2951</v>
-      </c>
-      <c r="D957" t="s">
-        <v>2952</v>
       </c>
       <c r="E957">
         <v>17400000</v>
@@ -48411,13 +48420,13 @@
         <v>957</v>
       </c>
       <c r="B958" t="s">
+        <v>2952</v>
+      </c>
+      <c r="C958" t="s">
         <v>2953</v>
       </c>
-      <c r="C958" t="s">
+      <c r="D958" t="s">
         <v>2954</v>
-      </c>
-      <c r="D958" t="s">
-        <v>2955</v>
       </c>
       <c r="E958">
         <v>23000000</v>
@@ -48452,13 +48461,13 @@
         <v>958</v>
       </c>
       <c r="B959" t="s">
+        <v>2955</v>
+      </c>
+      <c r="C959" t="s">
         <v>2956</v>
       </c>
-      <c r="C959" t="s">
+      <c r="D959" t="s">
         <v>2957</v>
-      </c>
-      <c r="D959" t="s">
-        <v>2958</v>
       </c>
       <c r="E959">
         <v>21000000</v>
@@ -48493,13 +48502,13 @@
         <v>959</v>
       </c>
       <c r="B960" t="s">
+        <v>2958</v>
+      </c>
+      <c r="C960" t="s">
         <v>2959</v>
       </c>
-      <c r="C960" t="s">
+      <c r="D960" t="s">
         <v>2960</v>
-      </c>
-      <c r="D960" t="s">
-        <v>2961</v>
       </c>
       <c r="E960">
         <v>121000000</v>
@@ -48531,13 +48540,13 @@
         <v>960</v>
       </c>
       <c r="B961" t="s">
+        <v>2961</v>
+      </c>
+      <c r="C961" t="s">
         <v>2962</v>
       </c>
-      <c r="C961" t="s">
+      <c r="D961" t="s">
         <v>2963</v>
-      </c>
-      <c r="D961" t="s">
-        <v>2964</v>
       </c>
       <c r="E961">
         <v>42000000</v>
@@ -48569,13 +48578,13 @@
         <v>961</v>
       </c>
       <c r="B962" t="s">
+        <v>2964</v>
+      </c>
+      <c r="C962" t="s">
         <v>2965</v>
       </c>
-      <c r="C962" t="s">
+      <c r="D962" t="s">
         <v>2966</v>
-      </c>
-      <c r="D962" t="s">
-        <v>2967</v>
       </c>
       <c r="E962">
         <v>55000000</v>
@@ -48584,7 +48593,7 @@
         <v>623</v>
       </c>
       <c r="G962" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="H962" t="s">
         <v>19</v>
@@ -48610,13 +48619,13 @@
         <v>962</v>
       </c>
       <c r="B963" t="s">
+        <v>2968</v>
+      </c>
+      <c r="C963" t="s">
         <v>2969</v>
       </c>
-      <c r="C963" t="s">
+      <c r="D963" t="s">
         <v>2970</v>
-      </c>
-      <c r="D963" t="s">
-        <v>2971</v>
       </c>
       <c r="E963">
         <v>24000000</v>
@@ -48648,13 +48657,13 @@
         <v>963</v>
       </c>
       <c r="B964" t="s">
+        <v>2971</v>
+      </c>
+      <c r="C964" t="s">
         <v>2972</v>
       </c>
-      <c r="C964" t="s">
+      <c r="D964" t="s">
         <v>2973</v>
-      </c>
-      <c r="D964" t="s">
-        <v>2974</v>
       </c>
       <c r="E964">
         <v>148000000</v>
@@ -48686,13 +48695,13 @@
         <v>964</v>
       </c>
       <c r="B965" t="s">
+        <v>2974</v>
+      </c>
+      <c r="C965" t="s">
         <v>2975</v>
       </c>
-      <c r="C965" t="s">
+      <c r="D965" t="s">
         <v>2976</v>
-      </c>
-      <c r="D965" t="s">
-        <v>2977</v>
       </c>
       <c r="E965">
         <v>70000000</v>
@@ -48727,13 +48736,13 @@
         <v>965</v>
       </c>
       <c r="B966" t="s">
+        <v>2977</v>
+      </c>
+      <c r="C966" t="s">
         <v>2978</v>
       </c>
-      <c r="C966" t="s">
+      <c r="D966" t="s">
         <v>2979</v>
-      </c>
-      <c r="D966" t="s">
-        <v>2980</v>
       </c>
       <c r="E966">
         <v>260000000</v>
@@ -48765,13 +48774,13 @@
         <v>966</v>
       </c>
       <c r="B967" t="s">
+        <v>2980</v>
+      </c>
+      <c r="C967" t="s">
         <v>2981</v>
       </c>
-      <c r="C967" t="s">
+      <c r="D967" t="s">
         <v>2982</v>
-      </c>
-      <c r="D967" t="s">
-        <v>2983</v>
       </c>
       <c r="E967">
         <v>193500000</v>
@@ -48806,13 +48815,13 @@
         <v>967</v>
       </c>
       <c r="B968" t="s">
+        <v>2983</v>
+      </c>
+      <c r="C968" t="s">
         <v>2984</v>
       </c>
-      <c r="C968" t="s">
+      <c r="D968" t="s">
         <v>2985</v>
-      </c>
-      <c r="D968" t="s">
-        <v>2986</v>
       </c>
       <c r="E968">
         <v>270000000</v>
@@ -48837,6 +48846,47 @@
       </c>
       <c r="M968">
         <v>100</v>
+      </c>
+    </row>
+    <row r="969" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A969">
+        <v>968</v>
+      </c>
+      <c r="B969" t="s">
+        <v>2987</v>
+      </c>
+      <c r="C969" t="s">
+        <v>2988</v>
+      </c>
+      <c r="D969" t="s">
+        <v>2989</v>
+      </c>
+      <c r="E969">
+        <v>50000000</v>
+      </c>
+      <c r="F969" t="s">
+        <v>117</v>
+      </c>
+      <c r="G969" t="s">
+        <v>289</v>
+      </c>
+      <c r="H969" t="s">
+        <v>19</v>
+      </c>
+      <c r="I969" t="s">
+        <v>35</v>
+      </c>
+      <c r="J969" s="1">
+        <v>46528</v>
+      </c>
+      <c r="L969">
+        <v>100</v>
+      </c>
+      <c r="M969">
+        <v>100</v>
+      </c>
+      <c r="N969" s="2">
+        <v>3.1E-2</v>
       </c>
     </row>
   </sheetData>

--- a/项目库.xlsx
+++ b/项目库.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\zhong\PyCharm\YKABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D51A8A1-FF27-46BA-AF92-F0278EB33D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82614337-FAB4-4F35-AE23-4053DF91ABE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B4AD8DE-DEA2-44E1-BABE-E39F8463801E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7265" uniqueCount="2990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7300" uniqueCount="3005">
   <si>
     <t>证券编号</t>
   </si>
@@ -9009,6 +9009,51 @@
   </si>
   <si>
     <t>268348.SH</t>
+  </si>
+  <si>
+    <t>建欣2026-6</t>
+  </si>
+  <si>
+    <t>26建欣6C</t>
+  </si>
+  <si>
+    <t>2689122.IB</t>
+  </si>
+  <si>
+    <t>建欣2026-4</t>
+  </si>
+  <si>
+    <t>26建欣4C</t>
+  </si>
+  <si>
+    <t>2689116.IB</t>
+  </si>
+  <si>
+    <t>建欣2026-5</t>
+  </si>
+  <si>
+    <t>26建欣5C</t>
+  </si>
+  <si>
+    <t>2689118.IB</t>
+  </si>
+  <si>
+    <t>交诚2026-2</t>
+  </si>
+  <si>
+    <t>26交诚2C</t>
+  </si>
+  <si>
+    <t>2689102.IB</t>
+  </si>
+  <si>
+    <t>邮盈惠丰2026-2</t>
+  </si>
+  <si>
+    <t>26邮盈惠丰2C</t>
+  </si>
+  <si>
+    <t>2689104.IB</t>
   </si>
 </sst>
 </file>
@@ -9407,7 +9452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C76155E-453F-4668-B0ED-1B0E36401906}">
-  <dimension ref="A1:N969"/>
+  <dimension ref="A1:N974"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="5" max="5" width="11.5625" bestFit="1" customWidth="1"/>
@@ -48889,6 +48934,196 @@
         <v>3.1E-2</v>
       </c>
     </row>
+    <row r="970" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A970">
+        <v>969</v>
+      </c>
+      <c r="B970" t="s">
+        <v>2990</v>
+      </c>
+      <c r="C970" t="s">
+        <v>2991</v>
+      </c>
+      <c r="D970" t="s">
+        <v>2992</v>
+      </c>
+      <c r="E970">
+        <v>97000000</v>
+      </c>
+      <c r="F970" t="s">
+        <v>27</v>
+      </c>
+      <c r="G970" t="s">
+        <v>43</v>
+      </c>
+      <c r="H970" t="s">
+        <v>29</v>
+      </c>
+      <c r="I970" t="s">
+        <v>35</v>
+      </c>
+      <c r="J970" s="1">
+        <v>47690</v>
+      </c>
+      <c r="L970">
+        <v>104</v>
+      </c>
+      <c r="M970">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="971" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A971">
+        <v>970</v>
+      </c>
+      <c r="B971" t="s">
+        <v>2993</v>
+      </c>
+      <c r="C971" t="s">
+        <v>2994</v>
+      </c>
+      <c r="D971" t="s">
+        <v>2995</v>
+      </c>
+      <c r="E971">
+        <v>137000000</v>
+      </c>
+      <c r="F971" t="s">
+        <v>27</v>
+      </c>
+      <c r="G971" t="s">
+        <v>43</v>
+      </c>
+      <c r="H971" t="s">
+        <v>29</v>
+      </c>
+      <c r="I971" t="s">
+        <v>35</v>
+      </c>
+      <c r="J971" s="1">
+        <v>47690</v>
+      </c>
+      <c r="L971">
+        <v>104</v>
+      </c>
+      <c r="M971">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="972" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A972">
+        <v>971</v>
+      </c>
+      <c r="B972" t="s">
+        <v>2996</v>
+      </c>
+      <c r="C972" t="s">
+        <v>2997</v>
+      </c>
+      <c r="D972" t="s">
+        <v>2998</v>
+      </c>
+      <c r="E972">
+        <v>64000000</v>
+      </c>
+      <c r="F972" t="s">
+        <v>56</v>
+      </c>
+      <c r="G972" t="s">
+        <v>43</v>
+      </c>
+      <c r="H972" t="s">
+        <v>29</v>
+      </c>
+      <c r="I972" t="s">
+        <v>35</v>
+      </c>
+      <c r="J972" s="1">
+        <v>49151</v>
+      </c>
+      <c r="L972">
+        <v>100</v>
+      </c>
+      <c r="M972">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="973" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A973">
+        <v>972</v>
+      </c>
+      <c r="B973" t="s">
+        <v>2999</v>
+      </c>
+      <c r="C973" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D973" t="s">
+        <v>3001</v>
+      </c>
+      <c r="E973">
+        <v>155000000</v>
+      </c>
+      <c r="F973" t="s">
+        <v>42</v>
+      </c>
+      <c r="G973" t="s">
+        <v>140</v>
+      </c>
+      <c r="H973" t="s">
+        <v>29</v>
+      </c>
+      <c r="I973" t="s">
+        <v>35</v>
+      </c>
+      <c r="J973" s="1">
+        <v>48117</v>
+      </c>
+      <c r="L973">
+        <v>102</v>
+      </c>
+      <c r="M973">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="974" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A974">
+        <v>973</v>
+      </c>
+      <c r="B974" t="s">
+        <v>3002</v>
+      </c>
+      <c r="C974" t="s">
+        <v>3003</v>
+      </c>
+      <c r="D974" t="s">
+        <v>3004</v>
+      </c>
+      <c r="E974">
+        <v>100000000</v>
+      </c>
+      <c r="F974" t="s">
+        <v>27</v>
+      </c>
+      <c r="G974" t="s">
+        <v>495</v>
+      </c>
+      <c r="H974" t="s">
+        <v>29</v>
+      </c>
+      <c r="I974" t="s">
+        <v>35</v>
+      </c>
+      <c r="J974" s="1">
+        <v>47234</v>
+      </c>
+      <c r="L974">
+        <v>103</v>
+      </c>
+      <c r="M974">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/项目库.xlsx
+++ b/项目库.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\zhong\PyCharm\YKABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82614337-FAB4-4F35-AE23-4053DF91ABE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B2B288-D11F-4AA4-9661-5C84BF0FA4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B4AD8DE-DEA2-44E1-BABE-E39F8463801E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{2B4AD8DE-DEA2-44E1-BABE-E39F8463801E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7300" uniqueCount="3005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7391" uniqueCount="3046">
   <si>
     <t>证券编号</t>
   </si>
@@ -9054,6 +9054,129 @@
   </si>
   <si>
     <t>2689104.IB</t>
+  </si>
+  <si>
+    <t>唯品会商业REITs</t>
+  </si>
+  <si>
+    <t>R唯品会2</t>
+  </si>
+  <si>
+    <t>508603.SH</t>
+  </si>
+  <si>
+    <t>公募Reits</t>
+  </si>
+  <si>
+    <t>盛赢4号第3期</t>
+  </si>
+  <si>
+    <t>盛赢43D</t>
+  </si>
+  <si>
+    <t>500817.SZ</t>
+  </si>
+  <si>
+    <t>惠元2026-4</t>
+  </si>
+  <si>
+    <t>26惠元4C</t>
+  </si>
+  <si>
+    <t>2689126.IB</t>
+  </si>
+  <si>
+    <t>鸿富2026-3</t>
+  </si>
+  <si>
+    <t>26鸿富3优先</t>
+  </si>
+  <si>
+    <t>2689123.IB</t>
+  </si>
+  <si>
+    <t>26鸿富3C</t>
+  </si>
+  <si>
+    <t>2689124.IB</t>
+  </si>
+  <si>
+    <t>招元和萃2026-4</t>
+  </si>
+  <si>
+    <t>26招元和萃4C</t>
+  </si>
+  <si>
+    <t>2689114.IB</t>
+  </si>
+  <si>
+    <t>尚赢2号9期</t>
+  </si>
+  <si>
+    <t>尚赢贰9C</t>
+  </si>
+  <si>
+    <t>268782.SH</t>
+  </si>
+  <si>
+    <t>邮盈惠兴2022-2</t>
+  </si>
+  <si>
+    <t>22邮盈惠兴2C</t>
+  </si>
+  <si>
+    <t>2289259.IB</t>
+  </si>
+  <si>
+    <t>尚亦2号第2期</t>
+  </si>
+  <si>
+    <t>尚亦022D</t>
+  </si>
+  <si>
+    <t>268766.SH</t>
+  </si>
+  <si>
+    <t>徐工机械第5期</t>
+  </si>
+  <si>
+    <t>徐工5次</t>
+  </si>
+  <si>
+    <t>500553.SZ</t>
+  </si>
+  <si>
+    <t>徐工机械</t>
+  </si>
+  <si>
+    <t>吾悦广场不动产</t>
+  </si>
+  <si>
+    <t>吾悦广场</t>
+  </si>
+  <si>
+    <t>267024.SH</t>
+  </si>
+  <si>
+    <t>机构间Reits</t>
+  </si>
+  <si>
+    <t>惠元2026-6</t>
+  </si>
+  <si>
+    <t>26惠元6C</t>
+  </si>
+  <si>
+    <t>2689130.IB</t>
+  </si>
+  <si>
+    <t>中誉至诚2026-5</t>
+  </si>
+  <si>
+    <t>26中誉至诚5C</t>
+  </si>
+  <si>
+    <t>2689120.IB</t>
   </si>
 </sst>
 </file>
@@ -9452,7 +9575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C76155E-453F-4668-B0ED-1B0E36401906}">
-  <dimension ref="A1:N974"/>
+  <dimension ref="A1:N987"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="5" max="5" width="11.5625" bestFit="1" customWidth="1"/>
@@ -49124,6 +49247,515 @@
         <v>103</v>
       </c>
     </row>
+    <row r="975" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A975">
+        <v>974</v>
+      </c>
+      <c r="B975" t="s">
+        <v>3005</v>
+      </c>
+      <c r="C975" t="s">
+        <v>3006</v>
+      </c>
+      <c r="D975" t="s">
+        <v>3007</v>
+      </c>
+      <c r="E975">
+        <v>7000000000</v>
+      </c>
+      <c r="F975" t="s">
+        <v>3008</v>
+      </c>
+      <c r="G975" t="s">
+        <v>2274</v>
+      </c>
+      <c r="H975" t="s">
+        <v>19</v>
+      </c>
+      <c r="I975" t="s">
+        <v>35</v>
+      </c>
+      <c r="J975" s="1">
+        <v>57498</v>
+      </c>
+      <c r="L975">
+        <v>100</v>
+      </c>
+      <c r="M975">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="976" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A976">
+        <v>975</v>
+      </c>
+      <c r="B976" t="s">
+        <v>3009</v>
+      </c>
+      <c r="C976" t="s">
+        <v>3010</v>
+      </c>
+      <c r="D976" t="s">
+        <v>3011</v>
+      </c>
+      <c r="E976">
+        <v>75000000</v>
+      </c>
+      <c r="F976" t="s">
+        <v>117</v>
+      </c>
+      <c r="G976" t="s">
+        <v>289</v>
+      </c>
+      <c r="H976" t="s">
+        <v>19</v>
+      </c>
+      <c r="I976" t="s">
+        <v>35</v>
+      </c>
+      <c r="J976" s="1">
+        <v>46810</v>
+      </c>
+      <c r="L976">
+        <v>100</v>
+      </c>
+      <c r="M976">
+        <v>100</v>
+      </c>
+      <c r="N976" s="2">
+        <v>4.5499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="977" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A977">
+        <v>976</v>
+      </c>
+      <c r="B977" t="s">
+        <v>3012</v>
+      </c>
+      <c r="C977" t="s">
+        <v>3013</v>
+      </c>
+      <c r="D977" t="s">
+        <v>3014</v>
+      </c>
+      <c r="E977">
+        <v>139000000</v>
+      </c>
+      <c r="F977" t="s">
+        <v>27</v>
+      </c>
+      <c r="G977" t="s">
+        <v>60</v>
+      </c>
+      <c r="H977" t="s">
+        <v>29</v>
+      </c>
+      <c r="I977" t="s">
+        <v>35</v>
+      </c>
+      <c r="J977" s="1">
+        <v>47228</v>
+      </c>
+      <c r="L977">
+        <v>106</v>
+      </c>
+      <c r="M977">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="978" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A978">
+        <v>977</v>
+      </c>
+      <c r="B978" t="s">
+        <v>3015</v>
+      </c>
+      <c r="C978" t="s">
+        <v>3016</v>
+      </c>
+      <c r="D978" t="s">
+        <v>3017</v>
+      </c>
+      <c r="E978">
+        <v>52000000</v>
+      </c>
+      <c r="F978" t="s">
+        <v>27</v>
+      </c>
+      <c r="G978" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H978" t="s">
+        <v>29</v>
+      </c>
+      <c r="I978" t="s">
+        <v>35</v>
+      </c>
+      <c r="J978" s="1">
+        <v>46866</v>
+      </c>
+      <c r="L978">
+        <v>100</v>
+      </c>
+      <c r="M978">
+        <v>100</v>
+      </c>
+      <c r="N978" s="2">
+        <v>1.6799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="979" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A979">
+        <v>978</v>
+      </c>
+      <c r="B979" t="s">
+        <v>3015</v>
+      </c>
+      <c r="C979" t="s">
+        <v>3018</v>
+      </c>
+      <c r="D979" t="s">
+        <v>3019</v>
+      </c>
+      <c r="E979">
+        <v>24200000</v>
+      </c>
+      <c r="F979" t="s">
+        <v>27</v>
+      </c>
+      <c r="G979" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H979" t="s">
+        <v>29</v>
+      </c>
+      <c r="I979" t="s">
+        <v>35</v>
+      </c>
+      <c r="J979" s="1">
+        <v>47322</v>
+      </c>
+      <c r="L979">
+        <v>106</v>
+      </c>
+      <c r="M979">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="980" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A980">
+        <v>979</v>
+      </c>
+      <c r="B980" t="s">
+        <v>3020</v>
+      </c>
+      <c r="C980" t="s">
+        <v>3021</v>
+      </c>
+      <c r="D980" t="s">
+        <v>3022</v>
+      </c>
+      <c r="E980">
+        <v>63000000</v>
+      </c>
+      <c r="F980" t="s">
+        <v>27</v>
+      </c>
+      <c r="G980" t="s">
+        <v>18</v>
+      </c>
+      <c r="H980" t="s">
+        <v>29</v>
+      </c>
+      <c r="I980" t="s">
+        <v>35</v>
+      </c>
+      <c r="J980" s="1">
+        <v>47325</v>
+      </c>
+      <c r="L980">
+        <v>107</v>
+      </c>
+      <c r="M980">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="981" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A981">
+        <v>980</v>
+      </c>
+      <c r="B981" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C981" t="s">
+        <v>3024</v>
+      </c>
+      <c r="D981" t="s">
+        <v>3025</v>
+      </c>
+      <c r="E981">
+        <v>105000000</v>
+      </c>
+      <c r="F981" t="s">
+        <v>117</v>
+      </c>
+      <c r="G981" t="s">
+        <v>289</v>
+      </c>
+      <c r="H981" t="s">
+        <v>19</v>
+      </c>
+      <c r="I981" t="s">
+        <v>35</v>
+      </c>
+      <c r="J981" s="1">
+        <v>46811</v>
+      </c>
+      <c r="L981">
+        <v>100</v>
+      </c>
+      <c r="M981">
+        <v>100</v>
+      </c>
+      <c r="N981" s="2">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="982" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A982">
+        <v>981</v>
+      </c>
+      <c r="B982" t="s">
+        <v>3026</v>
+      </c>
+      <c r="C982" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D982" t="s">
+        <v>3028</v>
+      </c>
+      <c r="E982">
+        <v>260000000</v>
+      </c>
+      <c r="F982" t="s">
+        <v>42</v>
+      </c>
+      <c r="G982" t="s">
+        <v>495</v>
+      </c>
+      <c r="H982" t="s">
+        <v>29</v>
+      </c>
+      <c r="I982" t="s">
+        <v>35</v>
+      </c>
+      <c r="J982" s="1">
+        <v>46594</v>
+      </c>
+      <c r="L982">
+        <v>116</v>
+      </c>
+      <c r="M982">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="983" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A983">
+        <v>982</v>
+      </c>
+      <c r="B983" t="s">
+        <v>3029</v>
+      </c>
+      <c r="C983" t="s">
+        <v>3030</v>
+      </c>
+      <c r="D983" t="s">
+        <v>3031</v>
+      </c>
+      <c r="E983">
+        <v>35000000</v>
+      </c>
+      <c r="F983" t="s">
+        <v>117</v>
+      </c>
+      <c r="G983" t="s">
+        <v>289</v>
+      </c>
+      <c r="H983" t="s">
+        <v>19</v>
+      </c>
+      <c r="I983" t="s">
+        <v>35</v>
+      </c>
+      <c r="J983" s="1">
+        <v>46720</v>
+      </c>
+      <c r="L983">
+        <v>100</v>
+      </c>
+      <c r="M983">
+        <v>100</v>
+      </c>
+      <c r="N983" s="2">
+        <v>5.3600000000000002E-2</v>
+      </c>
+    </row>
+    <row r="984" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A984">
+        <v>983</v>
+      </c>
+      <c r="B984" t="s">
+        <v>3032</v>
+      </c>
+      <c r="C984" t="s">
+        <v>3033</v>
+      </c>
+      <c r="D984" t="s">
+        <v>3034</v>
+      </c>
+      <c r="E984">
+        <v>240000000</v>
+      </c>
+      <c r="F984" t="s">
+        <v>103</v>
+      </c>
+      <c r="G984" t="s">
+        <v>3035</v>
+      </c>
+      <c r="H984" t="s">
+        <v>19</v>
+      </c>
+      <c r="I984" t="s">
+        <v>35</v>
+      </c>
+      <c r="J984" s="1">
+        <v>47932</v>
+      </c>
+      <c r="L984">
+        <v>100</v>
+      </c>
+      <c r="M984">
+        <v>100</v>
+      </c>
+      <c r="N984" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="985" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A985">
+        <v>984</v>
+      </c>
+      <c r="B985" t="s">
+        <v>3036</v>
+      </c>
+      <c r="C985" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D985" t="s">
+        <v>3038</v>
+      </c>
+      <c r="E985">
+        <v>616000000</v>
+      </c>
+      <c r="F985" t="s">
+        <v>3039</v>
+      </c>
+      <c r="G985" t="s">
+        <v>3037</v>
+      </c>
+      <c r="H985" t="s">
+        <v>19</v>
+      </c>
+      <c r="I985" t="s">
+        <v>35</v>
+      </c>
+      <c r="J985" s="1">
+        <v>54888</v>
+      </c>
+      <c r="L985">
+        <v>100</v>
+      </c>
+      <c r="M985">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="986" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A986">
+        <v>985</v>
+      </c>
+      <c r="B986" t="s">
+        <v>3040</v>
+      </c>
+      <c r="C986" t="s">
+        <v>3041</v>
+      </c>
+      <c r="D986" t="s">
+        <v>3042</v>
+      </c>
+      <c r="E986">
+        <v>200000000</v>
+      </c>
+      <c r="F986" t="s">
+        <v>42</v>
+      </c>
+      <c r="G986" t="s">
+        <v>60</v>
+      </c>
+      <c r="H986" t="s">
+        <v>29</v>
+      </c>
+      <c r="I986" t="s">
+        <v>35</v>
+      </c>
+      <c r="J986" s="1">
+        <v>48049</v>
+      </c>
+      <c r="L986">
+        <v>100</v>
+      </c>
+      <c r="M986">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="987" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A987">
+        <v>986</v>
+      </c>
+      <c r="B987" t="s">
+        <v>3043</v>
+      </c>
+      <c r="C987" t="s">
+        <v>3044</v>
+      </c>
+      <c r="D987" t="s">
+        <v>3045</v>
+      </c>
+      <c r="E987">
+        <v>425000000</v>
+      </c>
+      <c r="F987" t="s">
+        <v>42</v>
+      </c>
+      <c r="G987" t="s">
+        <v>67</v>
+      </c>
+      <c r="H987" t="s">
+        <v>29</v>
+      </c>
+      <c r="I987" t="s">
+        <v>35</v>
+      </c>
+      <c r="J987" s="1">
+        <v>48270</v>
+      </c>
+      <c r="L987">
+        <v>100</v>
+      </c>
+      <c r="M987">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/项目库.xlsx
+++ b/项目库.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\zhong\PyCharm\YKABS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B2B288-D11F-4AA4-9661-5C84BF0FA4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C6BB6D-FE0B-4C0E-8384-7A811C86A75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{2B4AD8DE-DEA2-44E1-BABE-E39F8463801E}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2B4AD8DE-DEA2-44E1-BABE-E39F8463801E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7391" uniqueCount="3046">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7412" uniqueCount="3055">
   <si>
     <t>证券编号</t>
   </si>
@@ -9177,6 +9177,33 @@
   </si>
   <si>
     <t>2689120.IB</t>
+  </si>
+  <si>
+    <t>建欣2026-7</t>
+  </si>
+  <si>
+    <t>26建欣7C</t>
+  </si>
+  <si>
+    <t>2689132.IB</t>
+  </si>
+  <si>
+    <t>兴瑞2025-9</t>
+  </si>
+  <si>
+    <t>25兴瑞9C</t>
+  </si>
+  <si>
+    <t>2589338.IB</t>
+  </si>
+  <si>
+    <t>诚瑞4期</t>
+  </si>
+  <si>
+    <t>诚瑞4B</t>
+  </si>
+  <si>
+    <t>268774.SH</t>
   </si>
 </sst>
 </file>
@@ -9575,7 +9602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C76155E-453F-4668-B0ED-1B0E36401906}">
-  <dimension ref="A1:N987"/>
+  <dimension ref="A1:N990"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="5" max="5" width="11.5625" bestFit="1" customWidth="1"/>
@@ -49756,6 +49783,123 @@
         <v>100</v>
       </c>
     </row>
+    <row r="988" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A988">
+        <v>987</v>
+      </c>
+      <c r="B988" t="s">
+        <v>3046</v>
+      </c>
+      <c r="C988" t="s">
+        <v>3047</v>
+      </c>
+      <c r="D988" t="s">
+        <v>3048</v>
+      </c>
+      <c r="E988">
+        <v>400000000</v>
+      </c>
+      <c r="F988" t="s">
+        <v>42</v>
+      </c>
+      <c r="G988" t="s">
+        <v>43</v>
+      </c>
+      <c r="H988" t="s">
+        <v>29</v>
+      </c>
+      <c r="I988" t="s">
+        <v>35</v>
+      </c>
+      <c r="J988" s="1">
+        <v>48786</v>
+      </c>
+      <c r="L988">
+        <v>100</v>
+      </c>
+      <c r="M988">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="989" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A989">
+        <v>988</v>
+      </c>
+      <c r="B989" t="s">
+        <v>3049</v>
+      </c>
+      <c r="C989" t="s">
+        <v>3050</v>
+      </c>
+      <c r="D989" t="s">
+        <v>3051</v>
+      </c>
+      <c r="E989">
+        <v>53000000</v>
+      </c>
+      <c r="F989" t="s">
+        <v>27</v>
+      </c>
+      <c r="G989" t="s">
+        <v>506</v>
+      </c>
+      <c r="H989" t="s">
+        <v>29</v>
+      </c>
+      <c r="I989" t="s">
+        <v>35</v>
+      </c>
+      <c r="J989" s="1">
+        <v>46960</v>
+      </c>
+      <c r="L989">
+        <v>105</v>
+      </c>
+      <c r="M989">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="990" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A990">
+        <v>989</v>
+      </c>
+      <c r="B990" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C990" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D990" t="s">
+        <v>3054</v>
+      </c>
+      <c r="E990">
+        <v>80000000</v>
+      </c>
+      <c r="F990" t="s">
+        <v>2887</v>
+      </c>
+      <c r="G990" t="s">
+        <v>624</v>
+      </c>
+      <c r="H990" t="s">
+        <v>19</v>
+      </c>
+      <c r="I990" t="s">
+        <v>35</v>
+      </c>
+      <c r="J990" s="1">
+        <v>46867</v>
+      </c>
+      <c r="L990">
+        <v>100</v>
+      </c>
+      <c r="M990">
+        <v>100</v>
+      </c>
+      <c r="N990" s="2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
